--- a/public/exports/29189803.xlsx
+++ b/public/exports/29189803.xlsx
@@ -14314,12 +14314,12 @@
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311041324</t>
+          <t xml:space="preserve">311041311</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Århus)</t>
         </is>
       </c>
       <c r="M191" t="inlineStr">
@@ -14554,12 +14554,12 @@
       </c>
       <c r="N194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -14989,7 +14989,7 @@
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311319330</t>
+          <t xml:space="preserve">311319327</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="K262" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624659</t>
+          <t xml:space="preserve">311624658</t>
         </is>
       </c>
       <c r="L262" t="inlineStr">
@@ -26089,7 +26089,7 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759941</t>
+          <t xml:space="preserve">311759970</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759941</t>
+          <t xml:space="preserve">311759970</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">

--- a/public/exports/29189803.xlsx
+++ b/public/exports/29189803.xlsx
@@ -26089,7 +26089,7 @@
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759970</t>
+          <t xml:space="preserve">311759941</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
@@ -26164,7 +26164,7 @@
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759970</t>
+          <t xml:space="preserve">311759941</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
